--- a/benchmarks/cre/penzance_one_rosslyn/reference/One_Rosslyn_Reference_Model.xlsx
+++ b/benchmarks/cre/penzance_one_rosslyn/reference/One_Rosslyn_Reference_Model.xlsx
@@ -2008,7 +2008,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P178"/>
+  <dimension ref="A1:P172"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -12136,415 +12136,49 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" t="n">
-        <v>164</v>
-      </c>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>2037-07</t>
-        </is>
-      </c>
-      <c r="C172" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D172" s="5">
-        <f>D171+C172</f>
-        <v/>
-      </c>
-      <c r="E172" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F172" s="5">
-        <f>F171+E172</f>
-        <v/>
-      </c>
-      <c r="G172" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H172" s="5">
-        <f>I171*Assumptions!$B$66/12</f>
-        <v/>
-      </c>
-      <c r="I172" s="5">
-        <f>I171+G172+H172</f>
-        <v/>
-      </c>
-      <c r="J172" t="n">
-        <v>733.4</v>
-      </c>
-      <c r="K172" s="5">
-        <f>J172*Assumptions!$B$47*(1+Assumptions!$B$49)^((A172-32)/12)</f>
-        <v/>
-      </c>
-      <c r="L172" s="5">
-        <f>J172*Assumptions!$B$48*0.5*(1+Assumptions!$B$49)^((A172-32)/12)</f>
-        <v/>
-      </c>
-      <c r="M172" s="5">
-        <f>J172*Assumptions!$B$45/12*(1+Assumptions!$B$49)^((A172-32)/12)</f>
-        <v/>
-      </c>
-      <c r="N172" s="5">
-        <f>K172+L172-M172</f>
-        <v/>
-      </c>
-      <c r="O172" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P172" s="5">
-        <f>N172+O172-C172</f>
-        <v/>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="n">
-        <v>165</v>
-      </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>2037-08</t>
-        </is>
-      </c>
-      <c r="C173" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D173" s="5">
-        <f>D172+C173</f>
-        <v/>
-      </c>
-      <c r="E173" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F173" s="5">
-        <f>F172+E173</f>
-        <v/>
-      </c>
-      <c r="G173" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H173" s="5">
-        <f>I172*Assumptions!$B$66/12</f>
-        <v/>
-      </c>
-      <c r="I173" s="5">
-        <f>I172+G173+H173</f>
-        <v/>
-      </c>
-      <c r="J173" t="n">
-        <v>733.4</v>
-      </c>
-      <c r="K173" s="5">
-        <f>J173*Assumptions!$B$47*(1+Assumptions!$B$49)^((A173-32)/12)</f>
-        <v/>
-      </c>
-      <c r="L173" s="5">
-        <f>J173*Assumptions!$B$48*0.5*(1+Assumptions!$B$49)^((A173-32)/12)</f>
-        <v/>
-      </c>
-      <c r="M173" s="5">
-        <f>J173*Assumptions!$B$45/12*(1+Assumptions!$B$49)^((A173-32)/12)</f>
-        <v/>
-      </c>
-      <c r="N173" s="5">
-        <f>K173+L173-M173</f>
-        <v/>
-      </c>
-      <c r="O173" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P173" s="5">
-        <f>N173+O173-C173</f>
-        <v/>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="n">
-        <v>166</v>
-      </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>2037-09</t>
-        </is>
-      </c>
-      <c r="C174" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D174" s="5">
-        <f>D173+C174</f>
-        <v/>
-      </c>
-      <c r="E174" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F174" s="5">
-        <f>F173+E174</f>
-        <v/>
-      </c>
-      <c r="G174" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H174" s="5">
-        <f>I173*Assumptions!$B$66/12</f>
-        <v/>
-      </c>
-      <c r="I174" s="5">
-        <f>I173+G174+H174</f>
-        <v/>
-      </c>
-      <c r="J174" t="n">
-        <v>733.4</v>
-      </c>
-      <c r="K174" s="5">
-        <f>J174*Assumptions!$B$47*(1+Assumptions!$B$49)^((A174-32)/12)</f>
-        <v/>
-      </c>
-      <c r="L174" s="5">
-        <f>J174*Assumptions!$B$48*0.5*(1+Assumptions!$B$49)^((A174-32)/12)</f>
-        <v/>
-      </c>
-      <c r="M174" s="5">
-        <f>J174*Assumptions!$B$45/12*(1+Assumptions!$B$49)^((A174-32)/12)</f>
-        <v/>
-      </c>
-      <c r="N174" s="5">
-        <f>K174+L174-M174</f>
-        <v/>
-      </c>
-      <c r="O174" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P174" s="5">
-        <f>N174+O174-C174</f>
-        <v/>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="n">
-        <v>167</v>
-      </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>2037-10</t>
-        </is>
-      </c>
-      <c r="C175" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D175" s="5">
-        <f>D174+C175</f>
-        <v/>
-      </c>
-      <c r="E175" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F175" s="5">
-        <f>F174+E175</f>
-        <v/>
-      </c>
-      <c r="G175" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H175" s="5">
-        <f>I174*Assumptions!$B$66/12</f>
-        <v/>
-      </c>
-      <c r="I175" s="5">
-        <f>I174+G175+H175</f>
-        <v/>
-      </c>
-      <c r="J175" t="n">
-        <v>733.4</v>
-      </c>
-      <c r="K175" s="5">
-        <f>J175*Assumptions!$B$47*(1+Assumptions!$B$49)^((A175-32)/12)</f>
-        <v/>
-      </c>
-      <c r="L175" s="5">
-        <f>J175*Assumptions!$B$48*0.5*(1+Assumptions!$B$49)^((A175-32)/12)</f>
-        <v/>
-      </c>
-      <c r="M175" s="5">
-        <f>J175*Assumptions!$B$45/12*(1+Assumptions!$B$49)^((A175-32)/12)</f>
-        <v/>
-      </c>
-      <c r="N175" s="5">
-        <f>K175+L175-M175</f>
-        <v/>
-      </c>
-      <c r="O175" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P175" s="5">
-        <f>N175+O175-C175</f>
-        <v/>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="n">
-        <v>168</v>
-      </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>2037-11</t>
-        </is>
-      </c>
-      <c r="C176" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D176" s="5">
-        <f>D175+C176</f>
-        <v/>
-      </c>
-      <c r="E176" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F176" s="5">
-        <f>F175+E176</f>
-        <v/>
-      </c>
-      <c r="G176" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H176" s="5">
-        <f>I175*Assumptions!$B$66/12</f>
-        <v/>
-      </c>
-      <c r="I176" s="5">
-        <f>I175+G176+H176</f>
-        <v/>
-      </c>
-      <c r="J176" t="n">
-        <v>733.4</v>
-      </c>
-      <c r="K176" s="5">
-        <f>J176*Assumptions!$B$47*(1+Assumptions!$B$49)^((A176-32)/12)</f>
-        <v/>
-      </c>
-      <c r="L176" s="5">
-        <f>J176*Assumptions!$B$48*0.5*(1+Assumptions!$B$49)^((A176-32)/12)</f>
-        <v/>
-      </c>
-      <c r="M176" s="5">
-        <f>J176*Assumptions!$B$45/12*(1+Assumptions!$B$49)^((A176-32)/12)</f>
-        <v/>
-      </c>
-      <c r="N176" s="5">
-        <f>K176+L176-M176</f>
-        <v/>
-      </c>
-      <c r="O176" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P176" s="5">
-        <f>N176+O176-C176</f>
-        <v/>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="n">
-        <v>169</v>
-      </c>
-      <c r="B177" t="inlineStr">
-        <is>
-          <t>2037-12</t>
-        </is>
-      </c>
-      <c r="C177" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D177" s="5">
-        <f>D176+C177</f>
-        <v/>
-      </c>
-      <c r="E177" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F177" s="5">
-        <f>F176+E177</f>
-        <v/>
-      </c>
-      <c r="G177" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H177" s="5">
-        <f>I176*Assumptions!$B$66/12</f>
-        <v/>
-      </c>
-      <c r="I177" s="5">
-        <f>I176+G177+H177</f>
-        <v/>
-      </c>
-      <c r="J177" t="n">
-        <v>733.4</v>
-      </c>
-      <c r="K177" s="5">
-        <f>J177*Assumptions!$B$47*(1+Assumptions!$B$49)^((A177-32)/12)</f>
-        <v/>
-      </c>
-      <c r="L177" s="5">
-        <f>J177*Assumptions!$B$48*0.5*(1+Assumptions!$B$49)^((A177-32)/12)</f>
-        <v/>
-      </c>
-      <c r="M177" s="5">
-        <f>J177*Assumptions!$B$45/12*(1+Assumptions!$B$49)^((A177-32)/12)</f>
-        <v/>
-      </c>
-      <c r="N177" s="5">
-        <f>K177+L177-M177</f>
-        <v/>
-      </c>
-      <c r="O177" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P177" s="5">
-        <f>N177+O177-C177</f>
-        <v/>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" s="1" t="inlineStr">
+      <c r="A172" s="1" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C178" s="9">
-        <f>SUM(C8:C177)</f>
-        <v/>
-      </c>
-      <c r="E178" s="9">
-        <f>SUM(E8:E177)</f>
-        <v/>
-      </c>
-      <c r="G178" s="9">
-        <f>SUM(G8:G177)</f>
-        <v/>
-      </c>
-      <c r="H178" s="9">
-        <f>SUM(H8:H177)</f>
-        <v/>
-      </c>
-      <c r="K178" s="9">
-        <f>SUM(K8:K177)</f>
-        <v/>
-      </c>
-      <c r="L178" s="9">
-        <f>SUM(L8:L177)</f>
-        <v/>
-      </c>
-      <c r="M178" s="9">
-        <f>SUM(M8:M177)</f>
-        <v/>
-      </c>
-      <c r="N178" s="9">
-        <f>SUM(N8:N177)</f>
-        <v/>
-      </c>
-      <c r="O178" s="9">
-        <f>SUM(O8:O177)</f>
-        <v/>
-      </c>
-      <c r="P178" s="9">
-        <f>SUM(P8:P177)</f>
+      <c r="C172" s="9">
+        <f>SUM(C8:C171)</f>
+        <v/>
+      </c>
+      <c r="E172" s="9">
+        <f>SUM(E8:E171)</f>
+        <v/>
+      </c>
+      <c r="G172" s="9">
+        <f>SUM(G8:G171)</f>
+        <v/>
+      </c>
+      <c r="H172" s="9">
+        <f>SUM(H8:H171)</f>
+        <v/>
+      </c>
+      <c r="K172" s="9">
+        <f>SUM(K8:K171)</f>
+        <v/>
+      </c>
+      <c r="L172" s="9">
+        <f>SUM(L8:L171)</f>
+        <v/>
+      </c>
+      <c r="M172" s="9">
+        <f>SUM(M8:M171)</f>
+        <v/>
+      </c>
+      <c r="N172" s="9">
+        <f>SUM(N8:N171)</f>
+        <v/>
+      </c>
+      <c r="O172" s="9">
+        <f>SUM(O8:O171)</f>
+        <v/>
+      </c>
+      <c r="P172" s="9">
+        <f>SUM(P8:P171)</f>
         <v/>
       </c>
     </row>
@@ -23829,7 +23463,7 @@
         <v>2183247.96</v>
       </c>
       <c r="K170" s="5" t="n">
-        <v>670867718.37</v>
+        <v>691127414.86</v>
       </c>
       <c r="L170" s="5" t="n">
         <v>324846432.07</v>
@@ -23838,7 +23472,7 @@
         <v>0</v>
       </c>
       <c r="N170" s="5" t="n">
-        <v>346926940.69</v>
+        <v>367186637.18</v>
       </c>
     </row>
     <row r="171">
@@ -24074,7 +23708,7 @@
         <v>567404297.9358341</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>670867718.3674999</v>
+        <v>691127414.856208</v>
       </c>
     </row>
     <row r="16">
@@ -24087,7 +23721,7 @@
         <v>734979.6605389999</v>
       </c>
       <c r="C16" s="5" t="n">
-        <v>868999.635191</v>
+        <v>895242.7653579999</v>
       </c>
     </row>
     <row r="17">
@@ -24118,7 +23752,7 @@
         <v>331838260.339476</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>506786085.948591</v>
+        <v>527045782.437299</v>
       </c>
     </row>
     <row r="20">
@@ -24131,7 +23765,7 @@
         <v>28591605.501435</v>
       </c>
       <c r="C20" s="5" t="n">
-        <v>203539431.11055</v>
+        <v>223799127.599258</v>
       </c>
     </row>
     <row r="21">
@@ -24144,7 +23778,7 @@
         <v>1.094285</v>
       </c>
       <c r="C21" s="11" t="n">
-        <v>1.671201</v>
+        <v>1.73801</v>
       </c>
     </row>
     <row r="22">
@@ -24157,7 +23791,7 @@
         <v>0.020841</v>
       </c>
       <c r="C22" s="6" t="n">
-        <v>0.062027</v>
+        <v>0.066484</v>
       </c>
     </row>
   </sheetData>
